--- a/ILLIA/Julio/ILLIA-Julio.xlsx
+++ b/ILLIA/Julio/ILLIA-Julio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\ILLIA\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23365D9D-253A-4EA8-B84D-E353D567E35C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3581B1D-F639-4675-A414-CB50BBEA2342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="186">
   <si>
     <t>TELEFONO: 11 5320-2676</t>
   </si>
@@ -583,6 +583,9 @@
   </si>
   <si>
     <t>Gasto particular 1A - Honorarios y envio carta documento</t>
+  </si>
+  <si>
+    <t>Gasto particular 5B - Carta Documento Rivarola Paola 5B</t>
   </si>
 </sst>
 </file>
@@ -598,7 +601,7 @@
     <numFmt numFmtId="168" formatCode="0.0"/>
     <numFmt numFmtId="169" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@"/>
     <numFmt numFmtId="170" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="174" formatCode="_-&quot;$&quot;\ * #,##0.0000_-;\-&quot;$&quot;\ * #,##0.0000_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
+    <numFmt numFmtId="171" formatCode="_-&quot;$&quot;\ * #,##0.0000_-;\-&quot;$&quot;\ * #,##0.0000_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
   </numFmts>
   <fonts count="35" x14ac:knownFonts="1">
     <font>
@@ -1558,7 +1561,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27"/>
     <xf numFmtId="9" fontId="30" fillId="0" borderId="27"/>
   </cellStyleXfs>
-  <cellXfs count="289">
+  <cellXfs count="288">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1876,7 +1879,6 @@
     <xf numFmtId="165" fontId="28" fillId="22" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="21" fillId="22" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="21" fillId="21" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="21" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="21" fillId="21" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="21" fillId="21" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="21" fillId="21" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1897,80 +1899,6 @@
     <xf numFmtId="167" fontId="21" fillId="23" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="21" fillId="23" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="21" fillId="23" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="27" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="7" fillId="14" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="7" fillId="14" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="7" fillId="7" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1983,35 +1911,109 @@
     <xf numFmtId="165" fontId="7" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="7" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="16" fillId="9" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="4" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="4" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="4" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="13" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="27" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2304,51 +2306,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="273"/>
-      <c r="B1" s="274"/>
-      <c r="C1" s="275"/>
-      <c r="D1" s="275"/>
-      <c r="E1" s="276"/>
+      <c r="A1" s="239"/>
+      <c r="B1" s="240"/>
+      <c r="C1" s="241"/>
+      <c r="D1" s="241"/>
+      <c r="E1" s="242"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="277"/>
-      <c r="B2" s="278" t="s">
+      <c r="A2" s="243"/>
+      <c r="B2" s="244" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="272"/>
-      <c r="D2" s="272"/>
-      <c r="E2" s="279"/>
+      <c r="C2" s="238"/>
+      <c r="D2" s="238"/>
+      <c r="E2" s="245"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="277"/>
-      <c r="B3" s="233" t="s">
+      <c r="A3" s="243"/>
+      <c r="B3" s="251" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="280"/>
-      <c r="D3" s="280"/>
-      <c r="E3" s="279"/>
+      <c r="C3" s="252"/>
+      <c r="D3" s="252"/>
+      <c r="E3" s="245"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:9" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="277"/>
-      <c r="B4" s="235"/>
-      <c r="C4" s="235"/>
-      <c r="D4" s="235"/>
-      <c r="E4" s="279"/>
+      <c r="A4" s="243"/>
+      <c r="B4" s="253"/>
+      <c r="C4" s="253"/>
+      <c r="D4" s="253"/>
+      <c r="E4" s="245"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
     </row>
     <row r="5" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="281" t="s">
+      <c r="A5" s="246" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -2356,36 +2358,36 @@
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
-      <c r="E5" s="282"/>
+      <c r="E5" s="247"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="283" t="s">
+      <c r="A6" s="248" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="C6" s="284"/>
-      <c r="D6" s="284" t="s">
+      <c r="C6" s="249"/>
+      <c r="D6" s="249" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="285"/>
+      <c r="E6" s="250"/>
       <c r="F6" s="1"/>
       <c r="G6" s="137"/>
       <c r="H6" s="137"/>
       <c r="I6" s="138"/>
     </row>
     <row r="7" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="286" t="s">
+      <c r="A7" s="267" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="287"/>
-      <c r="C7" s="287"/>
-      <c r="D7" s="287"/>
-      <c r="E7" s="288"/>
+      <c r="B7" s="268"/>
+      <c r="C7" s="268"/>
+      <c r="D7" s="268"/>
+      <c r="E7" s="269"/>
       <c r="F7" s="5"/>
       <c r="G7" s="139"/>
       <c r="H7" s="139"/>
@@ -2398,10 +2400,10 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
-      <c r="B9" s="239" t="s">
+      <c r="B9" s="259" t="s">
         <v>163</v>
       </c>
-      <c r="C9" s="234"/>
+      <c r="C9" s="260"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
@@ -2410,8 +2412,8 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
-      <c r="B10" s="234"/>
-      <c r="C10" s="234"/>
+      <c r="B10" s="260"/>
+      <c r="C10" s="260"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
@@ -2420,8 +2422,8 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
-      <c r="B11" s="234"/>
-      <c r="C11" s="234"/>
+      <c r="B11" s="260"/>
+      <c r="C11" s="260"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -2440,43 +2442,43 @@
       <c r="H13" s="1"/>
     </row>
     <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="244" t="s">
+      <c r="A14" s="270" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="234"/>
-      <c r="C14" s="234"/>
-      <c r="D14" s="234"/>
-      <c r="E14" s="234"/>
+      <c r="B14" s="260"/>
+      <c r="C14" s="260"/>
+      <c r="D14" s="260"/>
+      <c r="E14" s="260"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
     </row>
     <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="234"/>
-      <c r="B15" s="234"/>
-      <c r="C15" s="234"/>
-      <c r="D15" s="234"/>
-      <c r="E15" s="234"/>
+      <c r="A15" s="260"/>
+      <c r="B15" s="260"/>
+      <c r="C15" s="260"/>
+      <c r="D15" s="260"/>
+      <c r="E15" s="260"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
     </row>
     <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="234"/>
-      <c r="B16" s="234"/>
-      <c r="C16" s="234"/>
-      <c r="D16" s="234"/>
-      <c r="E16" s="234"/>
+      <c r="A16" s="260"/>
+      <c r="B16" s="260"/>
+      <c r="C16" s="260"/>
+      <c r="D16" s="260"/>
+      <c r="E16" s="260"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
     </row>
     <row r="17" spans="1:26" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="234"/>
-      <c r="B17" s="234"/>
-      <c r="C17" s="234"/>
-      <c r="D17" s="234"/>
-      <c r="E17" s="234"/>
+      <c r="A17" s="260"/>
+      <c r="B17" s="260"/>
+      <c r="C17" s="260"/>
+      <c r="D17" s="260"/>
+      <c r="E17" s="260"/>
     </row>
     <row r="18" spans="1:26" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
@@ -2892,7 +2894,7 @@
         <v>166</v>
       </c>
       <c r="C40" s="13"/>
-      <c r="D40" s="260">
+      <c r="D40" s="227">
         <v>30000</v>
       </c>
       <c r="E40" s="22"/>
@@ -2998,10 +3000,10 @@
       <c r="F43" s="1"/>
     </row>
     <row r="44" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="243" t="s">
+      <c r="A44" s="265" t="s">
         <v>21</v>
       </c>
-      <c r="B44" s="231"/>
+      <c r="B44" s="255"/>
       <c r="C44" s="25"/>
       <c r="D44" s="170">
         <v>56041.08</v>
@@ -3068,7 +3070,7 @@
       </c>
       <c r="B48" s="13"/>
       <c r="C48" s="31"/>
-      <c r="D48" s="261">
+      <c r="D48" s="228">
         <v>490822.07</v>
       </c>
       <c r="E48" s="147" t="s">
@@ -3141,7 +3143,7 @@
         <v>27</v>
       </c>
       <c r="C51" s="142"/>
-      <c r="D51" s="262">
+      <c r="D51" s="229">
         <v>4401.87</v>
       </c>
       <c r="E51" s="35" t="str">
@@ -3198,12 +3200,12 @@
       <c r="Z53" s="1"/>
     </row>
     <row r="54" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="242" t="s">
+      <c r="A54" s="264" t="s">
         <v>168</v>
       </c>
-      <c r="B54" s="231"/>
+      <c r="B54" s="255"/>
       <c r="C54" s="13"/>
-      <c r="D54" s="263">
+      <c r="D54" s="230">
         <v>108000</v>
       </c>
       <c r="E54" s="145" t="s">
@@ -3237,7 +3239,7 @@
       </c>
       <c r="B55" s="155"/>
       <c r="C55" s="13"/>
-      <c r="D55" s="263">
+      <c r="D55" s="230">
         <v>35000</v>
       </c>
       <c r="E55" s="134" t="s">
@@ -3271,7 +3273,7 @@
       </c>
       <c r="B56" s="124"/>
       <c r="C56" s="37"/>
-      <c r="D56" s="264">
+      <c r="D56" s="231">
         <v>20446.5</v>
       </c>
       <c r="E56" s="145" t="s">
@@ -3282,12 +3284,12 @@
       <c r="H56" s="38"/>
     </row>
     <row r="57" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="230" t="s">
+      <c r="A57" s="254" t="s">
         <v>180</v>
       </c>
-      <c r="B57" s="231"/>
+      <c r="B57" s="255"/>
       <c r="C57" s="37"/>
-      <c r="D57" s="265">
+      <c r="D57" s="232">
         <v>450000</v>
       </c>
       <c r="E57" s="134" t="s">
@@ -3298,12 +3300,12 @@
       <c r="H57" s="38"/>
     </row>
     <row r="58" spans="1:26" s="138" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="230" t="s">
+      <c r="A58" s="254" t="s">
         <v>182</v>
       </c>
-      <c r="B58" s="231"/>
+      <c r="B58" s="255"/>
       <c r="C58" s="37"/>
-      <c r="D58" s="265">
+      <c r="D58" s="232">
         <v>250000</v>
       </c>
       <c r="E58" s="134" t="s">
@@ -3314,10 +3316,10 @@
       <c r="H58" s="204"/>
     </row>
     <row r="59" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="230" t="s">
+      <c r="A59" s="254" t="s">
         <v>169</v>
       </c>
-      <c r="B59" s="231"/>
+      <c r="B59" s="255"/>
       <c r="C59" s="21"/>
       <c r="D59" s="169">
         <v>16994.62</v>
@@ -3348,10 +3350,10 @@
       <c r="Z59" s="1"/>
     </row>
     <row r="60" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="230" t="s">
+      <c r="A60" s="254" t="s">
         <v>32</v>
       </c>
-      <c r="B60" s="231"/>
+      <c r="B60" s="255"/>
       <c r="C60" s="21"/>
       <c r="D60" s="169"/>
       <c r="E60" s="146"/>
@@ -3370,8 +3372,8 @@
       <c r="H61" s="1"/>
     </row>
     <row r="62" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="242"/>
-      <c r="B62" s="231"/>
+      <c r="A62" s="264"/>
+      <c r="B62" s="255"/>
       <c r="C62" s="13"/>
       <c r="D62" s="170"/>
       <c r="E62" s="36"/>
@@ -3426,11 +3428,11 @@
       <c r="Z63" s="1"/>
     </row>
     <row r="64" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="230"/>
-      <c r="B64" s="236"/>
+      <c r="A64" s="254"/>
+      <c r="B64" s="256"/>
       <c r="C64" s="41"/>
-      <c r="D64" s="241"/>
-      <c r="E64" s="228"/>
+      <c r="D64" s="262"/>
+      <c r="E64" s="271"/>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
@@ -3454,11 +3456,11 @@
       <c r="Z64" s="1"/>
     </row>
     <row r="65" spans="1:26" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="237"/>
-      <c r="B65" s="238"/>
+      <c r="A65" s="257"/>
+      <c r="B65" s="258"/>
       <c r="C65" s="41"/>
-      <c r="D65" s="266"/>
-      <c r="E65" s="229"/>
+      <c r="D65" s="263"/>
+      <c r="E65" s="272"/>
       <c r="F65" s="1"/>
       <c r="G65" s="1"/>
       <c r="H65" s="1"/>
@@ -3482,8 +3484,8 @@
       <c r="Z65" s="1"/>
     </row>
     <row r="66" spans="1:26" ht="33" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="230"/>
-      <c r="B66" s="231"/>
+      <c r="A66" s="254"/>
+      <c r="B66" s="255"/>
       <c r="C66" s="13"/>
       <c r="D66" s="174"/>
       <c r="E66" s="42"/>
@@ -3510,8 +3512,8 @@
       <c r="Z66" s="1"/>
     </row>
     <row r="67" spans="1:26" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="230"/>
-      <c r="B67" s="231"/>
+      <c r="A67" s="254"/>
+      <c r="B67" s="255"/>
       <c r="C67" s="13"/>
       <c r="D67" s="174"/>
       <c r="E67" s="42"/>
@@ -3538,8 +3540,8 @@
       <c r="Z67" s="1"/>
     </row>
     <row r="68" spans="1:26" ht="33.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="230"/>
-      <c r="B68" s="231"/>
+      <c r="A68" s="254"/>
+      <c r="B68" s="255"/>
       <c r="C68" s="13"/>
       <c r="D68" s="174"/>
       <c r="E68" s="36"/>
@@ -3573,8 +3575,8 @@
       <c r="Z69" s="1"/>
     </row>
     <row r="70" spans="1:26" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="230"/>
-      <c r="B70" s="231"/>
+      <c r="A70" s="254"/>
+      <c r="B70" s="255"/>
       <c r="C70" s="13"/>
       <c r="D70" s="174"/>
       <c r="E70" s="36"/>
@@ -3629,8 +3631,8 @@
       <c r="Z71" s="1"/>
     </row>
     <row r="72" spans="1:26" ht="33.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="230"/>
-      <c r="B72" s="231"/>
+      <c r="A72" s="254"/>
+      <c r="B72" s="255"/>
       <c r="C72" s="13"/>
       <c r="D72" s="174"/>
       <c r="E72" s="45"/>
@@ -3657,8 +3659,8 @@
       <c r="Z72" s="1"/>
     </row>
     <row r="73" spans="1:26" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="230"/>
-      <c r="B73" s="231"/>
+      <c r="A73" s="254"/>
+      <c r="B73" s="255"/>
       <c r="C73" s="13"/>
       <c r="D73" s="174"/>
       <c r="E73" s="45"/>
@@ -3685,8 +3687,8 @@
       <c r="Z73" s="1"/>
     </row>
     <row r="74" spans="1:26" ht="36.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="232"/>
-      <c r="B74" s="231"/>
+      <c r="A74" s="266"/>
+      <c r="B74" s="255"/>
       <c r="C74" s="46"/>
       <c r="D74" s="174"/>
       <c r="E74" s="45"/>
@@ -3739,7 +3741,7 @@
       </c>
       <c r="B77" s="155"/>
       <c r="C77" s="13"/>
-      <c r="D77" s="263">
+      <c r="D77" s="230">
         <v>16000</v>
       </c>
       <c r="E77" s="134" t="s">
@@ -3768,15 +3770,15 @@
       <c r="Z77" s="1"/>
     </row>
     <row r="78" spans="1:26" ht="30.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="230"/>
-      <c r="B78" s="231"/>
+      <c r="A78" s="254"/>
+      <c r="B78" s="255"/>
       <c r="C78" s="48"/>
       <c r="D78" s="172"/>
       <c r="E78" s="49"/>
     </row>
     <row r="79" spans="1:26" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="232"/>
-      <c r="B79" s="231"/>
+      <c r="A79" s="266"/>
+      <c r="B79" s="255"/>
       <c r="C79" s="13"/>
       <c r="D79" s="172"/>
       <c r="E79" s="49"/>
@@ -3867,7 +3869,7 @@
       </c>
       <c r="B84" s="13"/>
       <c r="C84" s="13"/>
-      <c r="D84" s="267">
+      <c r="D84" s="233">
         <v>36306.839999999997</v>
       </c>
       <c r="E84" s="53"/>
@@ -3979,7 +3981,7 @@
       </c>
       <c r="F90" s="1"/>
       <c r="G90" s="202"/>
-      <c r="H90" s="271"/>
+      <c r="H90" s="237"/>
     </row>
     <row r="91" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="92" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4188,13 +4190,13 @@
       <c r="Z98" s="1"/>
     </row>
     <row r="99" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="268" t="s">
+      <c r="A99" s="234" t="s">
         <v>40</v>
       </c>
-      <c r="B99" s="268"/>
-      <c r="C99" s="268"/>
-      <c r="D99" s="268"/>
-      <c r="E99" s="269"/>
+      <c r="B99" s="234"/>
+      <c r="C99" s="234"/>
+      <c r="D99" s="234"/>
+      <c r="E99" s="235"/>
       <c r="F99" s="1"/>
       <c r="G99" s="1"/>
       <c r="H99" s="1"/>
@@ -4453,7 +4455,7 @@
       <c r="A112" s="133" t="s">
         <v>47</v>
       </c>
-      <c r="B112" s="270">
+      <c r="B112" s="236">
         <v>-29229.020000000717</v>
       </c>
       <c r="C112" s="72"/>
@@ -4563,9 +4565,14 @@
       </c>
       <c r="C118" s="71"/>
     </row>
-    <row r="119" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A119" s="76"/>
-      <c r="B119" s="74"/>
+    <row r="119" spans="1:26" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="76" t="s">
+        <v>185</v>
+      </c>
+      <c r="B119" s="74">
+        <f>-73204-17800</f>
+        <v>-91004</v>
+      </c>
       <c r="C119" s="71"/>
     </row>
     <row r="120" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4574,7 +4581,7 @@
       </c>
       <c r="B120" s="78">
         <f>SUM(B112:B119)</f>
-        <v>571743.1799999983</v>
+        <v>480739.1799999983</v>
       </c>
       <c r="C120" s="79"/>
     </row>
@@ -4741,16 +4748,16 @@
     <row r="130" spans="1:26" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="131" spans="1:26" ht="60.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="132" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="240" t="s">
+      <c r="A132" s="261" t="s">
         <v>56</v>
       </c>
-      <c r="B132" s="234"/>
-      <c r="C132" s="234"/>
+      <c r="B132" s="260"/>
+      <c r="C132" s="260"/>
     </row>
     <row r="133" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="234"/>
-      <c r="B133" s="234"/>
-      <c r="C133" s="234"/>
+      <c r="A133" s="260"/>
+      <c r="B133" s="260"/>
+      <c r="C133" s="260"/>
     </row>
     <row r="134" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="13"/>
@@ -5707,6 +5714,14 @@
     <row r="1005" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="E64:E65"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A73:B73"/>
     <mergeCell ref="B3:D4"/>
     <mergeCell ref="A57:B57"/>
     <mergeCell ref="A64:B65"/>
@@ -5723,14 +5738,6 @@
     <mergeCell ref="A54:B54"/>
     <mergeCell ref="A7:E7"/>
     <mergeCell ref="A14:E17"/>
-    <mergeCell ref="E64:E65"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="A66:B66"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A73:B73"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5771,16 +5778,16 @@
       <c r="C1" s="90"/>
       <c r="D1" s="90"/>
       <c r="E1" s="90"/>
-      <c r="F1" s="252"/>
-      <c r="G1" s="234"/>
-      <c r="H1" s="234"/>
-      <c r="I1" s="234"/>
-      <c r="J1" s="234"/>
-      <c r="K1" s="234"/>
-      <c r="L1" s="234"/>
-      <c r="M1" s="234"/>
-      <c r="N1" s="234"/>
-      <c r="O1" s="234"/>
+      <c r="F1" s="283"/>
+      <c r="G1" s="260"/>
+      <c r="H1" s="260"/>
+      <c r="I1" s="260"/>
+      <c r="J1" s="260"/>
+      <c r="K1" s="260"/>
+      <c r="L1" s="260"/>
+      <c r="M1" s="260"/>
+      <c r="N1" s="260"/>
+      <c r="O1" s="260"/>
       <c r="P1" s="90"/>
       <c r="Q1" s="90"/>
     </row>
@@ -5833,80 +5840,80 @@
       <c r="Q3" s="94"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="259" t="s">
+      <c r="A4" s="273" t="s">
         <v>59</v>
       </c>
-      <c r="B4" s="248" t="s">
+      <c r="B4" s="280" t="s">
         <v>60</v>
       </c>
-      <c r="C4" s="253" t="s">
+      <c r="C4" s="275" t="s">
         <v>61</v>
       </c>
-      <c r="D4" s="253" t="s">
+      <c r="D4" s="275" t="s">
         <v>62</v>
       </c>
-      <c r="E4" s="257" t="s">
+      <c r="E4" s="276" t="s">
         <v>63</v>
       </c>
-      <c r="F4" s="253" t="s">
+      <c r="F4" s="275" t="s">
         <v>64</v>
       </c>
-      <c r="G4" s="253" t="s">
+      <c r="G4" s="275" t="s">
         <v>65</v>
       </c>
-      <c r="H4" s="253" t="s">
+      <c r="H4" s="275" t="s">
         <v>66</v>
       </c>
-      <c r="I4" s="257" t="s">
+      <c r="I4" s="276" t="s">
         <v>67</v>
       </c>
-      <c r="J4" s="258" t="s">
+      <c r="J4" s="287" t="s">
         <v>68</v>
       </c>
-      <c r="K4" s="246" t="s">
+      <c r="K4" s="279" t="s">
         <v>69</v>
       </c>
-      <c r="L4" s="250" t="s">
+      <c r="L4" s="282" t="s">
         <v>70</v>
       </c>
-      <c r="M4" s="246" t="s">
+      <c r="M4" s="279" t="s">
         <v>71</v>
       </c>
-      <c r="N4" s="254" t="s">
+      <c r="N4" s="284" t="s">
         <v>72</v>
       </c>
       <c r="O4" s="95" t="s">
         <v>73</v>
       </c>
-      <c r="P4" s="256" t="s">
+      <c r="P4" s="286" t="s">
         <v>74</v>
       </c>
-      <c r="Q4" s="250" t="s">
+      <c r="Q4" s="282" t="s">
         <v>75</v>
       </c>
       <c r="R4" s="1"/>
     </row>
     <row r="5" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="251"/>
-      <c r="B5" s="249"/>
-      <c r="C5" s="251"/>
-      <c r="D5" s="251"/>
-      <c r="E5" s="247"/>
-      <c r="F5" s="251"/>
-      <c r="G5" s="251"/>
-      <c r="H5" s="251"/>
-      <c r="I5" s="247"/>
-      <c r="J5" s="247"/>
-      <c r="K5" s="247"/>
-      <c r="L5" s="251"/>
-      <c r="M5" s="247"/>
-      <c r="N5" s="255"/>
+      <c r="A5" s="274"/>
+      <c r="B5" s="281"/>
+      <c r="C5" s="274"/>
+      <c r="D5" s="274"/>
+      <c r="E5" s="277"/>
+      <c r="F5" s="274"/>
+      <c r="G5" s="274"/>
+      <c r="H5" s="274"/>
+      <c r="I5" s="277"/>
+      <c r="J5" s="277"/>
+      <c r="K5" s="277"/>
+      <c r="L5" s="274"/>
+      <c r="M5" s="277"/>
+      <c r="N5" s="285"/>
       <c r="O5" s="96" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 14/08</v>
       </c>
-      <c r="P5" s="249"/>
-      <c r="Q5" s="251"/>
+      <c r="P5" s="281"/>
+      <c r="Q5" s="274"/>
     </row>
     <row r="6" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
@@ -7458,20 +7465,21 @@
         <f t="shared" si="5"/>
         <v>207000.00000000003</v>
       </c>
-      <c r="N30" s="213">
-        <v>0</v>
-      </c>
-      <c r="O30" s="214">
+      <c r="N30" s="198">
+        <f>73204+17800</f>
+        <v>91004</v>
+      </c>
+      <c r="O30" s="213">
         <f t="shared" si="6"/>
-        <v>664470.25</v>
-      </c>
-      <c r="P30" s="215">
+        <v>755474.25</v>
+      </c>
+      <c r="P30" s="214">
         <f t="shared" si="2"/>
-        <v>704338.25</v>
-      </c>
-      <c r="Q30" s="216">
+        <v>800803.25</v>
+      </c>
+      <c r="Q30" s="215">
         <f t="shared" si="3"/>
-        <v>684404.25</v>
+        <v>778138.25</v>
       </c>
       <c r="R30" s="61">
         <f t="shared" si="7"/>
@@ -7609,55 +7617,55 @@
       <c r="A33" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="B33" s="217" t="s">
+      <c r="B33" s="216" t="s">
         <v>156</v>
       </c>
-      <c r="C33" s="218">
+      <c r="C33" s="217">
         <f t="shared" si="8"/>
         <v>21</v>
       </c>
-      <c r="D33" s="218" t="s">
+      <c r="D33" s="217" t="s">
         <v>157</v>
       </c>
-      <c r="E33" s="219" t="s">
+      <c r="E33" s="218" t="s">
         <v>158</v>
       </c>
-      <c r="F33" s="220">
+      <c r="F33" s="219">
         <v>4.5</v>
       </c>
-      <c r="G33" s="221">
+      <c r="G33" s="220">
         <v>760335.28</v>
       </c>
-      <c r="H33" s="222">
+      <c r="H33" s="221">
         <v>200000</v>
       </c>
-      <c r="I33" s="223"/>
-      <c r="J33" s="224">
+      <c r="I33" s="222"/>
+      <c r="J33" s="223">
         <f t="shared" si="0"/>
         <v>560335.28</v>
       </c>
-      <c r="K33" s="224">
+      <c r="K33" s="223">
         <f t="shared" si="1"/>
         <v>16810.058400000002</v>
       </c>
-      <c r="L33" s="221">
+      <c r="L33" s="220">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M33" s="224">
+      <c r="M33" s="223">
         <f t="shared" si="5"/>
         <v>135000</v>
       </c>
-      <c r="N33" s="225"/>
-      <c r="O33" s="226">
+      <c r="N33" s="224"/>
+      <c r="O33" s="225">
         <f t="shared" si="6"/>
         <v>712145.28</v>
       </c>
-      <c r="P33" s="225">
+      <c r="P33" s="224">
         <f t="shared" si="2"/>
         <v>754874.28</v>
       </c>
-      <c r="Q33" s="227">
+      <c r="Q33" s="226">
         <f t="shared" si="3"/>
         <v>733509.28</v>
       </c>
@@ -7851,19 +7859,19 @@
       </c>
       <c r="N37" s="117">
         <f t="shared" si="9"/>
-        <v>91004</v>
+        <v>182008</v>
       </c>
       <c r="O37" s="118">
         <f t="shared" si="9"/>
-        <v>6003563.3499999996</v>
+        <v>6094567.3499999996</v>
       </c>
       <c r="P37" s="118">
         <f t="shared" si="9"/>
-        <v>6363778.6500000004</v>
+        <v>6460243.6500000004</v>
       </c>
       <c r="Q37" s="118">
         <f t="shared" si="9"/>
-        <v>6183671.3499999996</v>
+        <v>6277405.3499999996</v>
       </c>
     </row>
     <row r="38" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7880,95 +7888,95 @@
       <c r="Q39" s="1"/>
     </row>
     <row r="40" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D40" s="245" t="s">
+      <c r="D40" s="278" t="s">
         <v>183</v>
       </c>
-      <c r="E40" s="234"/>
-      <c r="F40" s="234"/>
-      <c r="G40" s="234"/>
-      <c r="H40" s="234"/>
-      <c r="I40" s="234"/>
-      <c r="J40" s="234"/>
-      <c r="K40" s="234"/>
-      <c r="L40" s="234"/>
-      <c r="M40" s="234"/>
-      <c r="N40" s="234"/>
-      <c r="O40" s="234"/>
+      <c r="E40" s="260"/>
+      <c r="F40" s="260"/>
+      <c r="G40" s="260"/>
+      <c r="H40" s="260"/>
+      <c r="I40" s="260"/>
+      <c r="J40" s="260"/>
+      <c r="K40" s="260"/>
+      <c r="L40" s="260"/>
+      <c r="M40" s="260"/>
+      <c r="N40" s="260"/>
+      <c r="O40" s="260"/>
       <c r="Q40" s="1"/>
     </row>
     <row r="41" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D41" s="234"/>
-      <c r="E41" s="234"/>
-      <c r="F41" s="234"/>
-      <c r="G41" s="234"/>
-      <c r="H41" s="234"/>
-      <c r="I41" s="234"/>
-      <c r="J41" s="234"/>
-      <c r="K41" s="234"/>
-      <c r="L41" s="234"/>
-      <c r="M41" s="234"/>
-      <c r="N41" s="234"/>
-      <c r="O41" s="234"/>
+      <c r="D41" s="260"/>
+      <c r="E41" s="260"/>
+      <c r="F41" s="260"/>
+      <c r="G41" s="260"/>
+      <c r="H41" s="260"/>
+      <c r="I41" s="260"/>
+      <c r="J41" s="260"/>
+      <c r="K41" s="260"/>
+      <c r="L41" s="260"/>
+      <c r="M41" s="260"/>
+      <c r="N41" s="260"/>
+      <c r="O41" s="260"/>
       <c r="Q41" s="1"/>
     </row>
     <row r="42" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D42" s="234"/>
-      <c r="E42" s="234"/>
-      <c r="F42" s="234"/>
-      <c r="G42" s="234"/>
-      <c r="H42" s="234"/>
-      <c r="I42" s="234"/>
-      <c r="J42" s="234"/>
-      <c r="K42" s="234"/>
-      <c r="L42" s="234"/>
-      <c r="M42" s="234"/>
-      <c r="N42" s="234"/>
-      <c r="O42" s="234"/>
+      <c r="D42" s="260"/>
+      <c r="E42" s="260"/>
+      <c r="F42" s="260"/>
+      <c r="G42" s="260"/>
+      <c r="H42" s="260"/>
+      <c r="I42" s="260"/>
+      <c r="J42" s="260"/>
+      <c r="K42" s="260"/>
+      <c r="L42" s="260"/>
+      <c r="M42" s="260"/>
+      <c r="N42" s="260"/>
+      <c r="O42" s="260"/>
       <c r="Q42" s="1"/>
     </row>
     <row r="43" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D43" s="234"/>
-      <c r="E43" s="234"/>
-      <c r="F43" s="234"/>
-      <c r="G43" s="234"/>
-      <c r="H43" s="234"/>
-      <c r="I43" s="234"/>
-      <c r="J43" s="234"/>
-      <c r="K43" s="234"/>
-      <c r="L43" s="234"/>
-      <c r="M43" s="234"/>
-      <c r="N43" s="234"/>
-      <c r="O43" s="234"/>
+      <c r="D43" s="260"/>
+      <c r="E43" s="260"/>
+      <c r="F43" s="260"/>
+      <c r="G43" s="260"/>
+      <c r="H43" s="260"/>
+      <c r="I43" s="260"/>
+      <c r="J43" s="260"/>
+      <c r="K43" s="260"/>
+      <c r="L43" s="260"/>
+      <c r="M43" s="260"/>
+      <c r="N43" s="260"/>
+      <c r="O43" s="260"/>
       <c r="Q43" s="1"/>
     </row>
     <row r="44" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D44" s="234"/>
-      <c r="E44" s="234"/>
-      <c r="F44" s="234"/>
-      <c r="G44" s="234"/>
-      <c r="H44" s="234"/>
-      <c r="I44" s="234"/>
-      <c r="J44" s="234"/>
-      <c r="K44" s="234"/>
-      <c r="L44" s="234"/>
-      <c r="M44" s="234"/>
-      <c r="N44" s="234"/>
-      <c r="O44" s="234"/>
+      <c r="D44" s="260"/>
+      <c r="E44" s="260"/>
+      <c r="F44" s="260"/>
+      <c r="G44" s="260"/>
+      <c r="H44" s="260"/>
+      <c r="I44" s="260"/>
+      <c r="J44" s="260"/>
+      <c r="K44" s="260"/>
+      <c r="L44" s="260"/>
+      <c r="M44" s="260"/>
+      <c r="N44" s="260"/>
+      <c r="O44" s="260"/>
       <c r="Q44" s="1"/>
     </row>
     <row r="45" spans="1:18" ht="108" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D45" s="234"/>
-      <c r="E45" s="234"/>
-      <c r="F45" s="234"/>
-      <c r="G45" s="234"/>
-      <c r="H45" s="234"/>
-      <c r="I45" s="234"/>
-      <c r="J45" s="234"/>
-      <c r="K45" s="234"/>
-      <c r="L45" s="234"/>
-      <c r="M45" s="234"/>
-      <c r="N45" s="234"/>
-      <c r="O45" s="234"/>
+      <c r="D45" s="260"/>
+      <c r="E45" s="260"/>
+      <c r="F45" s="260"/>
+      <c r="G45" s="260"/>
+      <c r="H45" s="260"/>
+      <c r="I45" s="260"/>
+      <c r="J45" s="260"/>
+      <c r="K45" s="260"/>
+      <c r="L45" s="260"/>
+      <c r="M45" s="260"/>
+      <c r="N45" s="260"/>
+      <c r="O45" s="260"/>
       <c r="Q45" s="1"/>
     </row>
     <row r="46" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13439,11 +13447,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="G4:G5"/>
     <mergeCell ref="D40:O45"/>
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="B4:B5"/>
@@ -13457,6 +13460,11 @@
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="J4:J5"/>
     <mergeCell ref="K4:K5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="G4:G5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>

--- a/ILLIA/Julio/ILLIA-Julio.xlsx
+++ b/ILLIA/Julio/ILLIA-Julio.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\ILLIA\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3581B1D-F639-4675-A414-CB50BBEA2342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C7F62A8-F5F3-409E-8368-91AE89D3BA44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1933,15 +1933,22 @@
     <xf numFmtId="0" fontId="5" fillId="13" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
@@ -1962,9 +1969,6 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1973,27 +1977,13 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2001,8 +1991,12 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2011,8 +2005,14 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2329,11 +2329,11 @@
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="243"/>
-      <c r="B3" s="251" t="s">
+      <c r="B3" s="256" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="252"/>
-      <c r="D3" s="252"/>
+      <c r="C3" s="257"/>
+      <c r="D3" s="257"/>
       <c r="E3" s="245"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
@@ -2341,9 +2341,9 @@
     </row>
     <row r="4" spans="1:9" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="243"/>
-      <c r="B4" s="253"/>
-      <c r="C4" s="253"/>
-      <c r="D4" s="253"/>
+      <c r="B4" s="258"/>
+      <c r="C4" s="258"/>
+      <c r="D4" s="258"/>
       <c r="E4" s="245"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
@@ -2381,13 +2381,13 @@
       <c r="I6" s="138"/>
     </row>
     <row r="7" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="267" t="s">
+      <c r="A7" s="269" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="268"/>
-      <c r="C7" s="268"/>
-      <c r="D7" s="268"/>
-      <c r="E7" s="269"/>
+      <c r="B7" s="270"/>
+      <c r="C7" s="270"/>
+      <c r="D7" s="270"/>
+      <c r="E7" s="271"/>
       <c r="F7" s="5"/>
       <c r="G7" s="139"/>
       <c r="H7" s="139"/>
@@ -2400,10 +2400,10 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
-      <c r="B9" s="259" t="s">
+      <c r="B9" s="262" t="s">
         <v>163</v>
       </c>
-      <c r="C9" s="260"/>
+      <c r="C9" s="263"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
@@ -2412,8 +2412,8 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
-      <c r="B10" s="260"/>
-      <c r="C10" s="260"/>
+      <c r="B10" s="263"/>
+      <c r="C10" s="263"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
@@ -2422,8 +2422,8 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
-      <c r="B11" s="260"/>
-      <c r="C11" s="260"/>
+      <c r="B11" s="263"/>
+      <c r="C11" s="263"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -2442,43 +2442,43 @@
       <c r="H13" s="1"/>
     </row>
     <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="270" t="s">
+      <c r="A14" s="272" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="260"/>
-      <c r="C14" s="260"/>
-      <c r="D14" s="260"/>
-      <c r="E14" s="260"/>
+      <c r="B14" s="263"/>
+      <c r="C14" s="263"/>
+      <c r="D14" s="263"/>
+      <c r="E14" s="263"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
     </row>
     <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="260"/>
-      <c r="B15" s="260"/>
-      <c r="C15" s="260"/>
-      <c r="D15" s="260"/>
-      <c r="E15" s="260"/>
+      <c r="A15" s="263"/>
+      <c r="B15" s="263"/>
+      <c r="C15" s="263"/>
+      <c r="D15" s="263"/>
+      <c r="E15" s="263"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
     </row>
     <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="260"/>
-      <c r="B16" s="260"/>
-      <c r="C16" s="260"/>
-      <c r="D16" s="260"/>
-      <c r="E16" s="260"/>
+      <c r="A16" s="263"/>
+      <c r="B16" s="263"/>
+      <c r="C16" s="263"/>
+      <c r="D16" s="263"/>
+      <c r="E16" s="263"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
     </row>
     <row r="17" spans="1:26" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="260"/>
-      <c r="B17" s="260"/>
-      <c r="C17" s="260"/>
-      <c r="D17" s="260"/>
-      <c r="E17" s="260"/>
+      <c r="A17" s="263"/>
+      <c r="B17" s="263"/>
+      <c r="C17" s="263"/>
+      <c r="D17" s="263"/>
+      <c r="E17" s="263"/>
     </row>
     <row r="18" spans="1:26" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
@@ -3000,10 +3000,10 @@
       <c r="F43" s="1"/>
     </row>
     <row r="44" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="265" t="s">
+      <c r="A44" s="268" t="s">
         <v>21</v>
       </c>
-      <c r="B44" s="255"/>
+      <c r="B44" s="254"/>
       <c r="C44" s="25"/>
       <c r="D44" s="170">
         <v>56041.08</v>
@@ -3200,10 +3200,10 @@
       <c r="Z53" s="1"/>
     </row>
     <row r="54" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="264" t="s">
+      <c r="A54" s="267" t="s">
         <v>168</v>
       </c>
-      <c r="B54" s="255"/>
+      <c r="B54" s="254"/>
       <c r="C54" s="13"/>
       <c r="D54" s="230">
         <v>108000</v>
@@ -3284,10 +3284,10 @@
       <c r="H56" s="38"/>
     </row>
     <row r="57" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="254" t="s">
+      <c r="A57" s="253" t="s">
         <v>180</v>
       </c>
-      <c r="B57" s="255"/>
+      <c r="B57" s="254"/>
       <c r="C57" s="37"/>
       <c r="D57" s="232">
         <v>450000</v>
@@ -3300,10 +3300,10 @@
       <c r="H57" s="38"/>
     </row>
     <row r="58" spans="1:26" s="138" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="254" t="s">
+      <c r="A58" s="253" t="s">
         <v>182</v>
       </c>
-      <c r="B58" s="255"/>
+      <c r="B58" s="254"/>
       <c r="C58" s="37"/>
       <c r="D58" s="232">
         <v>250000</v>
@@ -3316,10 +3316,10 @@
       <c r="H58" s="204"/>
     </row>
     <row r="59" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="254" t="s">
+      <c r="A59" s="253" t="s">
         <v>169</v>
       </c>
-      <c r="B59" s="255"/>
+      <c r="B59" s="254"/>
       <c r="C59" s="21"/>
       <c r="D59" s="169">
         <v>16994.62</v>
@@ -3350,10 +3350,10 @@
       <c r="Z59" s="1"/>
     </row>
     <row r="60" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="254" t="s">
+      <c r="A60" s="253" t="s">
         <v>32</v>
       </c>
-      <c r="B60" s="255"/>
+      <c r="B60" s="254"/>
       <c r="C60" s="21"/>
       <c r="D60" s="169"/>
       <c r="E60" s="146"/>
@@ -3372,8 +3372,8 @@
       <c r="H61" s="1"/>
     </row>
     <row r="62" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="264"/>
-      <c r="B62" s="255"/>
+      <c r="A62" s="267"/>
+      <c r="B62" s="254"/>
       <c r="C62" s="13"/>
       <c r="D62" s="170"/>
       <c r="E62" s="36"/>
@@ -3428,11 +3428,11 @@
       <c r="Z63" s="1"/>
     </row>
     <row r="64" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="254"/>
-      <c r="B64" s="256"/>
+      <c r="A64" s="253"/>
+      <c r="B64" s="259"/>
       <c r="C64" s="41"/>
-      <c r="D64" s="262"/>
-      <c r="E64" s="271"/>
+      <c r="D64" s="265"/>
+      <c r="E64" s="251"/>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
@@ -3456,11 +3456,11 @@
       <c r="Z64" s="1"/>
     </row>
     <row r="65" spans="1:26" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="257"/>
-      <c r="B65" s="258"/>
+      <c r="A65" s="260"/>
+      <c r="B65" s="261"/>
       <c r="C65" s="41"/>
-      <c r="D65" s="263"/>
-      <c r="E65" s="272"/>
+      <c r="D65" s="266"/>
+      <c r="E65" s="252"/>
       <c r="F65" s="1"/>
       <c r="G65" s="1"/>
       <c r="H65" s="1"/>
@@ -3484,8 +3484,8 @@
       <c r="Z65" s="1"/>
     </row>
     <row r="66" spans="1:26" ht="33" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="254"/>
-      <c r="B66" s="255"/>
+      <c r="A66" s="253"/>
+      <c r="B66" s="254"/>
       <c r="C66" s="13"/>
       <c r="D66" s="174"/>
       <c r="E66" s="42"/>
@@ -3512,8 +3512,8 @@
       <c r="Z66" s="1"/>
     </row>
     <row r="67" spans="1:26" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="254"/>
-      <c r="B67" s="255"/>
+      <c r="A67" s="253"/>
+      <c r="B67" s="254"/>
       <c r="C67" s="13"/>
       <c r="D67" s="174"/>
       <c r="E67" s="42"/>
@@ -3540,8 +3540,8 @@
       <c r="Z67" s="1"/>
     </row>
     <row r="68" spans="1:26" ht="33.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="254"/>
-      <c r="B68" s="255"/>
+      <c r="A68" s="253"/>
+      <c r="B68" s="254"/>
       <c r="C68" s="13"/>
       <c r="D68" s="174"/>
       <c r="E68" s="36"/>
@@ -3575,8 +3575,8 @@
       <c r="Z69" s="1"/>
     </row>
     <row r="70" spans="1:26" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="254"/>
-      <c r="B70" s="255"/>
+      <c r="A70" s="253"/>
+      <c r="B70" s="254"/>
       <c r="C70" s="13"/>
       <c r="D70" s="174"/>
       <c r="E70" s="36"/>
@@ -3631,8 +3631,8 @@
       <c r="Z71" s="1"/>
     </row>
     <row r="72" spans="1:26" ht="33.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="254"/>
-      <c r="B72" s="255"/>
+      <c r="A72" s="253"/>
+      <c r="B72" s="254"/>
       <c r="C72" s="13"/>
       <c r="D72" s="174"/>
       <c r="E72" s="45"/>
@@ -3659,8 +3659,8 @@
       <c r="Z72" s="1"/>
     </row>
     <row r="73" spans="1:26" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="254"/>
-      <c r="B73" s="255"/>
+      <c r="A73" s="253"/>
+      <c r="B73" s="254"/>
       <c r="C73" s="13"/>
       <c r="D73" s="174"/>
       <c r="E73" s="45"/>
@@ -3687,8 +3687,8 @@
       <c r="Z73" s="1"/>
     </row>
     <row r="74" spans="1:26" ht="36.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="266"/>
-      <c r="B74" s="255"/>
+      <c r="A74" s="255"/>
+      <c r="B74" s="254"/>
       <c r="C74" s="46"/>
       <c r="D74" s="174"/>
       <c r="E74" s="45"/>
@@ -3770,15 +3770,15 @@
       <c r="Z77" s="1"/>
     </row>
     <row r="78" spans="1:26" ht="30.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="254"/>
-      <c r="B78" s="255"/>
+      <c r="A78" s="253"/>
+      <c r="B78" s="254"/>
       <c r="C78" s="48"/>
       <c r="D78" s="172"/>
       <c r="E78" s="49"/>
     </row>
     <row r="79" spans="1:26" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="266"/>
-      <c r="B79" s="255"/>
+      <c r="A79" s="255"/>
+      <c r="B79" s="254"/>
       <c r="C79" s="13"/>
       <c r="D79" s="172"/>
       <c r="E79" s="49"/>
@@ -4748,16 +4748,16 @@
     <row r="130" spans="1:26" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="131" spans="1:26" ht="60.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="132" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="261" t="s">
+      <c r="A132" s="264" t="s">
         <v>56</v>
       </c>
-      <c r="B132" s="260"/>
-      <c r="C132" s="260"/>
+      <c r="B132" s="263"/>
+      <c r="C132" s="263"/>
     </row>
     <row r="133" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="260"/>
-      <c r="B133" s="260"/>
-      <c r="C133" s="260"/>
+      <c r="A133" s="263"/>
+      <c r="B133" s="263"/>
+      <c r="C133" s="263"/>
     </row>
     <row r="134" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="13"/>
@@ -5714,14 +5714,6 @@
     <row r="1005" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="E64:E65"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="A66:B66"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A73:B73"/>
     <mergeCell ref="B3:D4"/>
     <mergeCell ref="A57:B57"/>
     <mergeCell ref="A64:B65"/>
@@ -5738,6 +5730,14 @@
     <mergeCell ref="A54:B54"/>
     <mergeCell ref="A7:E7"/>
     <mergeCell ref="A14:E17"/>
+    <mergeCell ref="E64:E65"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A73:B73"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5778,16 +5778,16 @@
       <c r="C1" s="90"/>
       <c r="D1" s="90"/>
       <c r="E1" s="90"/>
-      <c r="F1" s="283"/>
-      <c r="G1" s="260"/>
-      <c r="H1" s="260"/>
-      <c r="I1" s="260"/>
-      <c r="J1" s="260"/>
-      <c r="K1" s="260"/>
-      <c r="L1" s="260"/>
-      <c r="M1" s="260"/>
-      <c r="N1" s="260"/>
-      <c r="O1" s="260"/>
+      <c r="F1" s="280"/>
+      <c r="G1" s="263"/>
+      <c r="H1" s="263"/>
+      <c r="I1" s="263"/>
+      <c r="J1" s="263"/>
+      <c r="K1" s="263"/>
+      <c r="L1" s="263"/>
+      <c r="M1" s="263"/>
+      <c r="N1" s="263"/>
+      <c r="O1" s="263"/>
       <c r="P1" s="90"/>
       <c r="Q1" s="90"/>
     </row>
@@ -5840,80 +5840,80 @@
       <c r="Q3" s="94"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="273" t="s">
+      <c r="A4" s="287" t="s">
         <v>59</v>
       </c>
-      <c r="B4" s="280" t="s">
+      <c r="B4" s="276" t="s">
         <v>60</v>
       </c>
-      <c r="C4" s="275" t="s">
+      <c r="C4" s="281" t="s">
         <v>61</v>
       </c>
-      <c r="D4" s="275" t="s">
+      <c r="D4" s="281" t="s">
         <v>62</v>
       </c>
-      <c r="E4" s="276" t="s">
+      <c r="E4" s="285" t="s">
         <v>63</v>
       </c>
-      <c r="F4" s="275" t="s">
+      <c r="F4" s="281" t="s">
         <v>64</v>
       </c>
-      <c r="G4" s="275" t="s">
+      <c r="G4" s="281" t="s">
         <v>65</v>
       </c>
-      <c r="H4" s="275" t="s">
+      <c r="H4" s="281" t="s">
         <v>66</v>
       </c>
-      <c r="I4" s="276" t="s">
+      <c r="I4" s="285" t="s">
         <v>67</v>
       </c>
-      <c r="J4" s="287" t="s">
+      <c r="J4" s="286" t="s">
         <v>68</v>
       </c>
-      <c r="K4" s="279" t="s">
+      <c r="K4" s="274" t="s">
         <v>69</v>
       </c>
-      <c r="L4" s="282" t="s">
+      <c r="L4" s="278" t="s">
         <v>70</v>
       </c>
-      <c r="M4" s="279" t="s">
+      <c r="M4" s="274" t="s">
         <v>71</v>
       </c>
-      <c r="N4" s="284" t="s">
+      <c r="N4" s="282" t="s">
         <v>72</v>
       </c>
       <c r="O4" s="95" t="s">
         <v>73</v>
       </c>
-      <c r="P4" s="286" t="s">
+      <c r="P4" s="284" t="s">
         <v>74</v>
       </c>
-      <c r="Q4" s="282" t="s">
+      <c r="Q4" s="278" t="s">
         <v>75</v>
       </c>
       <c r="R4" s="1"/>
     </row>
     <row r="5" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="274"/>
-      <c r="B5" s="281"/>
-      <c r="C5" s="274"/>
-      <c r="D5" s="274"/>
-      <c r="E5" s="277"/>
-      <c r="F5" s="274"/>
-      <c r="G5" s="274"/>
-      <c r="H5" s="274"/>
-      <c r="I5" s="277"/>
-      <c r="J5" s="277"/>
-      <c r="K5" s="277"/>
-      <c r="L5" s="274"/>
-      <c r="M5" s="277"/>
-      <c r="N5" s="285"/>
+      <c r="A5" s="279"/>
+      <c r="B5" s="277"/>
+      <c r="C5" s="279"/>
+      <c r="D5" s="279"/>
+      <c r="E5" s="275"/>
+      <c r="F5" s="279"/>
+      <c r="G5" s="279"/>
+      <c r="H5" s="279"/>
+      <c r="I5" s="275"/>
+      <c r="J5" s="275"/>
+      <c r="K5" s="275"/>
+      <c r="L5" s="279"/>
+      <c r="M5" s="275"/>
+      <c r="N5" s="283"/>
       <c r="O5" s="96" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 14/08</v>
       </c>
-      <c r="P5" s="281"/>
-      <c r="Q5" s="274"/>
+      <c r="P5" s="277"/>
+      <c r="Q5" s="279"/>
     </row>
     <row r="6" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
@@ -7644,10 +7644,7 @@
         <f t="shared" si="0"/>
         <v>560335.28</v>
       </c>
-      <c r="K33" s="223">
-        <f t="shared" si="1"/>
-        <v>16810.058400000002</v>
-      </c>
+      <c r="K33" s="223"/>
       <c r="L33" s="220">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -7659,15 +7656,15 @@
       <c r="N33" s="224"/>
       <c r="O33" s="225">
         <f t="shared" si="6"/>
-        <v>712145.28</v>
+        <v>695335.28</v>
       </c>
       <c r="P33" s="224">
         <f t="shared" si="2"/>
-        <v>754874.28</v>
+        <v>737055.28</v>
       </c>
       <c r="Q33" s="226">
         <f t="shared" si="3"/>
-        <v>733509.28</v>
+        <v>716195.28</v>
       </c>
       <c r="R33" s="61">
         <f t="shared" si="7"/>
@@ -7847,7 +7844,7 @@
       </c>
       <c r="K37" s="116">
         <f t="shared" si="9"/>
-        <v>85281.290999999997</v>
+        <v>68471.232599999988</v>
       </c>
       <c r="L37" s="117">
         <f t="shared" si="9"/>
@@ -7863,15 +7860,15 @@
       </c>
       <c r="O37" s="118">
         <f t="shared" si="9"/>
-        <v>6094567.3499999996</v>
+        <v>6077757.3499999996</v>
       </c>
       <c r="P37" s="118">
         <f t="shared" si="9"/>
-        <v>6460243.6500000004</v>
+        <v>6442424.6500000004</v>
       </c>
       <c r="Q37" s="118">
         <f t="shared" si="9"/>
-        <v>6277405.3499999996</v>
+        <v>6260091.3499999996</v>
       </c>
     </row>
     <row r="38" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7888,95 +7885,95 @@
       <c r="Q39" s="1"/>
     </row>
     <row r="40" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D40" s="278" t="s">
+      <c r="D40" s="273" t="s">
         <v>183</v>
       </c>
-      <c r="E40" s="260"/>
-      <c r="F40" s="260"/>
-      <c r="G40" s="260"/>
-      <c r="H40" s="260"/>
-      <c r="I40" s="260"/>
-      <c r="J40" s="260"/>
-      <c r="K40" s="260"/>
-      <c r="L40" s="260"/>
-      <c r="M40" s="260"/>
-      <c r="N40" s="260"/>
-      <c r="O40" s="260"/>
+      <c r="E40" s="263"/>
+      <c r="F40" s="263"/>
+      <c r="G40" s="263"/>
+      <c r="H40" s="263"/>
+      <c r="I40" s="263"/>
+      <c r="J40" s="263"/>
+      <c r="K40" s="263"/>
+      <c r="L40" s="263"/>
+      <c r="M40" s="263"/>
+      <c r="N40" s="263"/>
+      <c r="O40" s="263"/>
       <c r="Q40" s="1"/>
     </row>
     <row r="41" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D41" s="260"/>
-      <c r="E41" s="260"/>
-      <c r="F41" s="260"/>
-      <c r="G41" s="260"/>
-      <c r="H41" s="260"/>
-      <c r="I41" s="260"/>
-      <c r="J41" s="260"/>
-      <c r="K41" s="260"/>
-      <c r="L41" s="260"/>
-      <c r="M41" s="260"/>
-      <c r="N41" s="260"/>
-      <c r="O41" s="260"/>
+      <c r="D41" s="263"/>
+      <c r="E41" s="263"/>
+      <c r="F41" s="263"/>
+      <c r="G41" s="263"/>
+      <c r="H41" s="263"/>
+      <c r="I41" s="263"/>
+      <c r="J41" s="263"/>
+      <c r="K41" s="263"/>
+      <c r="L41" s="263"/>
+      <c r="M41" s="263"/>
+      <c r="N41" s="263"/>
+      <c r="O41" s="263"/>
       <c r="Q41" s="1"/>
     </row>
     <row r="42" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D42" s="260"/>
-      <c r="E42" s="260"/>
-      <c r="F42" s="260"/>
-      <c r="G42" s="260"/>
-      <c r="H42" s="260"/>
-      <c r="I42" s="260"/>
-      <c r="J42" s="260"/>
-      <c r="K42" s="260"/>
-      <c r="L42" s="260"/>
-      <c r="M42" s="260"/>
-      <c r="N42" s="260"/>
-      <c r="O42" s="260"/>
+      <c r="D42" s="263"/>
+      <c r="E42" s="263"/>
+      <c r="F42" s="263"/>
+      <c r="G42" s="263"/>
+      <c r="H42" s="263"/>
+      <c r="I42" s="263"/>
+      <c r="J42" s="263"/>
+      <c r="K42" s="263"/>
+      <c r="L42" s="263"/>
+      <c r="M42" s="263"/>
+      <c r="N42" s="263"/>
+      <c r="O42" s="263"/>
       <c r="Q42" s="1"/>
     </row>
     <row r="43" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D43" s="260"/>
-      <c r="E43" s="260"/>
-      <c r="F43" s="260"/>
-      <c r="G43" s="260"/>
-      <c r="H43" s="260"/>
-      <c r="I43" s="260"/>
-      <c r="J43" s="260"/>
-      <c r="K43" s="260"/>
-      <c r="L43" s="260"/>
-      <c r="M43" s="260"/>
-      <c r="N43" s="260"/>
-      <c r="O43" s="260"/>
+      <c r="D43" s="263"/>
+      <c r="E43" s="263"/>
+      <c r="F43" s="263"/>
+      <c r="G43" s="263"/>
+      <c r="H43" s="263"/>
+      <c r="I43" s="263"/>
+      <c r="J43" s="263"/>
+      <c r="K43" s="263"/>
+      <c r="L43" s="263"/>
+      <c r="M43" s="263"/>
+      <c r="N43" s="263"/>
+      <c r="O43" s="263"/>
       <c r="Q43" s="1"/>
     </row>
     <row r="44" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D44" s="260"/>
-      <c r="E44" s="260"/>
-      <c r="F44" s="260"/>
-      <c r="G44" s="260"/>
-      <c r="H44" s="260"/>
-      <c r="I44" s="260"/>
-      <c r="J44" s="260"/>
-      <c r="K44" s="260"/>
-      <c r="L44" s="260"/>
-      <c r="M44" s="260"/>
-      <c r="N44" s="260"/>
-      <c r="O44" s="260"/>
+      <c r="D44" s="263"/>
+      <c r="E44" s="263"/>
+      <c r="F44" s="263"/>
+      <c r="G44" s="263"/>
+      <c r="H44" s="263"/>
+      <c r="I44" s="263"/>
+      <c r="J44" s="263"/>
+      <c r="K44" s="263"/>
+      <c r="L44" s="263"/>
+      <c r="M44" s="263"/>
+      <c r="N44" s="263"/>
+      <c r="O44" s="263"/>
       <c r="Q44" s="1"/>
     </row>
     <row r="45" spans="1:18" ht="108" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D45" s="260"/>
-      <c r="E45" s="260"/>
-      <c r="F45" s="260"/>
-      <c r="G45" s="260"/>
-      <c r="H45" s="260"/>
-      <c r="I45" s="260"/>
-      <c r="J45" s="260"/>
-      <c r="K45" s="260"/>
-      <c r="L45" s="260"/>
-      <c r="M45" s="260"/>
-      <c r="N45" s="260"/>
-      <c r="O45" s="260"/>
+      <c r="D45" s="263"/>
+      <c r="E45" s="263"/>
+      <c r="F45" s="263"/>
+      <c r="G45" s="263"/>
+      <c r="H45" s="263"/>
+      <c r="I45" s="263"/>
+      <c r="J45" s="263"/>
+      <c r="K45" s="263"/>
+      <c r="L45" s="263"/>
+      <c r="M45" s="263"/>
+      <c r="N45" s="263"/>
+      <c r="O45" s="263"/>
       <c r="Q45" s="1"/>
     </row>
     <row r="46" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13447,6 +13444,11 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="G4:G5"/>
     <mergeCell ref="D40:O45"/>
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="B4:B5"/>
@@ -13460,11 +13462,6 @@
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="J4:J5"/>
     <mergeCell ref="K4:K5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="G4:G5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
